--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -491,11 +491,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>34.5</v>
+        <v>35.8</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -527,10 +527,10 @@
         <v>69</v>
       </c>
       <c r="L2" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="M2" t="n">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -544,7 +544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -576,6 +576,38 @@
       <c r="F1" t="inlineStr">
         <is>
           <t>Detalles</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Temperatura máxima</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>35.8 °C</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>06/08/2026</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>34.5 °C (2026-08-06)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>TempMax 35.8°C / TempMin 21.9°C / Racha 19.8 km/h / Lluvia 0.0 mm / Presión 1017.95-1019.98 hPa</t>
         </is>
       </c>
     </row>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -491,11 +491,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>35.8</v>
+        <v>39.5</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -507,11 +507,11 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>19.8</v>
+        <v>26.1</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -521,16 +521,16 @@
         <v>1019.98</v>
       </c>
       <c r="J2" t="n">
-        <v>1017.95</v>
+        <v>1017.27</v>
       </c>
       <c r="K2" t="n">
         <v>69</v>
       </c>
       <c r="L2" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="M2" t="n">
-        <v>157</v>
+        <v>287</v>
       </c>
     </row>
   </sheetData>
@@ -544,7 +544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,6 +608,102 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>TempMax 35.8°C / TempMin 21.9°C / Racha 19.8 km/h / Lluvia 0.0 mm / Presión 1017.95-1019.98 hPa</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Temperatura máxima</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>39.5 °C</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>06/08/2026</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>35.8 °C (2026-08-06)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>TempMax 39.5°C / TempMin 21.9°C / Racha 26.1 km/h / Lluvia 0.0 mm / Presión 1017.27-1019.98 hPa</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Racha de viento</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>26.1 km/h</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>06/08/2026</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>19.8 km/h (2026-08-06)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>TempMax 39.5°C / TempMin 21.9°C / Racha 26.1 km/h / Lluvia 0.0 mm / Presión 1017.27-1019.98 hPa</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Presión mínima</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1017.27 hPa</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>06/08/2026</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1017.95 hPa (2026-08-06)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>TempMax 39.5°C / TempMin 21.9°C / Racha 26.1 km/h / Lluvia 0.0 mm / Presión 1017.27-1019.98 hPa</t>
         </is>
       </c>
     </row>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -530,6 +530,55 @@
         <v>22</v>
       </c>
       <c r="M2" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1019.3</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1015.24</v>
+      </c>
+      <c r="K3" t="n">
+        <v>49</v>
+      </c>
+      <c r="L3" t="n">
+        <v>21</v>
+      </c>
+      <c r="M3" t="n">
         <v>287</v>
       </c>
     </row>
@@ -544,7 +593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -707,6 +756,102 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Temperatura máxima</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>39.7 °C</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>39.5 °C (2026-08-06)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>TempMax 39.7°C / TempMin 23.3°C / Racha 29.3 km/h / Lluvia 0.0 mm / Presión 1015.24-1019.3 hPa</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Racha de viento</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>29.3 km/h</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>26.1 km/h (2026-08-06)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>TempMax 39.7°C / TempMin 23.3°C / Racha 29.3 km/h / Lluvia 0.0 mm / Presión 1015.24-1019.3 hPa</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Presión mínima</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1015.24 hPa</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1017.27 hPa (2026-08-06)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>TempMax 39.7°C / TempMin 23.3°C / Racha 29.3 km/h / Lluvia 0.0 mm / Presión 1015.24-1019.3 hPa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -579,6 +579,55 @@
         <v>21</v>
       </c>
       <c r="M3" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>08/08/2026</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>06:34</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1017.27</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1014.22</v>
+      </c>
+      <c r="K4" t="n">
+        <v>52</v>
+      </c>
+      <c r="L4" t="n">
+        <v>22</v>
+      </c>
+      <c r="M4" t="n">
         <v>287</v>
       </c>
     </row>
@@ -593,7 +642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -852,6 +901,102 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Temperatura máxima</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>40.6 °C</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>08/08/2026</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>39.7 °C (2026-08-07)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>TempMax 40.6°C / TempMin 24.5°C / Racha 36.5 km/h / Lluvia 0.0 mm / Presión 1014.22-1017.27 hPa</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Racha de viento</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>36.5 km/h</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>08/08/2026</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>29.3 km/h (2026-08-07)</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>TempMax 40.6°C / TempMin 24.5°C / Racha 36.5 km/h / Lluvia 0.0 mm / Presión 1014.22-1017.27 hPa</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Presión mínima</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1014.22 hPa</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>08/08/2026</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>1015.24 hPa (2026-08-07)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>TempMax 40.6°C / TempMin 24.5°C / Racha 36.5 km/h / Lluvia 0.0 mm / Presión 1014.22-1017.27 hPa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -628,6 +628,55 @@
         <v>22</v>
       </c>
       <c r="M4" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>09/08/2026</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>07:34</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1016.26</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1014.22</v>
+      </c>
+      <c r="K5" t="n">
+        <v>54</v>
+      </c>
+      <c r="L5" t="n">
+        <v>19</v>
+      </c>
+      <c r="M5" t="n">
         <v>287</v>
       </c>
     </row>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:P6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,6 +480,21 @@
       </c>
       <c r="M1" t="inlineStr">
         <is>
+          <t>Radiación Máx (W/m²)</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Hora Radiación</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>UV Máx</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
           <t>Nº Observaciones</t>
         </is>
       </c>
@@ -677,6 +692,66 @@
         <v>19</v>
       </c>
       <c r="M5" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>08:29</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>18:49</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1017.27</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1014.22</v>
+      </c>
+      <c r="K6" t="n">
+        <v>57</v>
+      </c>
+      <c r="L6" t="n">
+        <v>22</v>
+      </c>
+      <c r="M6" t="n">
+        <v>816.2</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>10</v>
+      </c>
+      <c r="P6" t="n">
         <v>287</v>
       </c>
     </row>
@@ -691,7 +766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1046,6 +1121,38 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Temperatura mínima</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>20.8 °C</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>08:29</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>21.9 °C (2026-08-06)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>TempMax 36.4°C / TempMin 20.8°C / Racha 28.5 km/h / Lluvia 0.0 mm / Presión 1014.22-1017.27 hPa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -752,6 +752,66 @@
         <v>10</v>
       </c>
       <c r="P6" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>19</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1017.27</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1014.22</v>
+      </c>
+      <c r="K7" t="n">
+        <v>50</v>
+      </c>
+      <c r="L7" t="n">
+        <v>10</v>
+      </c>
+      <c r="M7" t="n">
+        <v>804.7</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>10</v>
+      </c>
+      <c r="P7" t="n">
         <v>287</v>
       </c>
     </row>
@@ -766,7 +826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1153,6 +1213,38 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Temperatura máxima</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>41.1 °C</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>40.6 °C (2026-08-08)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>TempMax 41.1°C / TempMin 20.8°C / Racha 19.0 km/h / Lluvia 0.0 mm / Presión 1014.22-1017.27 hPa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:P8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -812,6 +812,66 @@
         <v>10</v>
       </c>
       <c r="P7" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>12/08/2026</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>25</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>05:54</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>19:03</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1019.3</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1016.26</v>
+      </c>
+      <c r="K8" t="n">
+        <v>45</v>
+      </c>
+      <c r="L8" t="n">
+        <v>10</v>
+      </c>
+      <c r="M8" t="n">
+        <v>790.5</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>10</v>
+      </c>
+      <c r="P8" t="n">
         <v>287</v>
       </c>
     </row>
@@ -826,7 +886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1245,6 +1305,38 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Temperatura máxima</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>42.5 °C</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>12/08/2026</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>41.1 °C (2026-08-11)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>TempMax 42.5°C / TempMin 25.0°C / Racha 26.1 km/h / Lluvia 0.0 mm / Presión 1016.26-1019.3 hPa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P8"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -872,6 +872,66 @@
         <v>10</v>
       </c>
       <c r="P8" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>13/08/2026</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>25</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>07:59</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>18:44</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1019.98</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1017.27</v>
+      </c>
+      <c r="K9" t="n">
+        <v>61</v>
+      </c>
+      <c r="L9" t="n">
+        <v>19</v>
+      </c>
+      <c r="M9" t="n">
+        <v>773.5</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>10</v>
+      </c>
+      <c r="P9" t="n">
         <v>287</v>
       </c>
     </row>
@@ -886,7 +946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1337,6 +1397,38 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Temperatura máxima</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>43.6 °C</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>13/08/2026</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>42.5 °C (2026-08-12)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>TempMax 43.6°C / TempMin 25.0°C / Racha 30.1 km/h / Lluvia 0.0 mm / Presión 1017.27-1019.98 hPa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -932,6 +932,66 @@
         <v>10</v>
       </c>
       <c r="P9" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>25</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>04:39</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1019.64</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1013.55</v>
+      </c>
+      <c r="K10" t="n">
+        <v>70</v>
+      </c>
+      <c r="L10" t="n">
+        <v>24</v>
+      </c>
+      <c r="M10" t="n">
+        <v>816.2</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>10</v>
+      </c>
+      <c r="P10" t="n">
         <v>287</v>
       </c>
     </row>
@@ -946,7 +1006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1429,6 +1489,38 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Presión mínima</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1013.55 hPa</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1014.22 hPa (2026-08-08)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>TempMax 40.3°C / TempMin 25.0°C / Racha 27.7 km/h / Lluvia 3.3 mm / Presión 1013.55-1019.64 hPa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -993,6 +993,66 @@
       </c>
       <c r="P10" t="n">
         <v>287</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>15/08/2026</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>23:49</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>17:54</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1015.92</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1011.18</v>
+      </c>
+      <c r="K11" t="n">
+        <v>79</v>
+      </c>
+      <c r="L11" t="n">
+        <v>37</v>
+      </c>
+      <c r="M11" t="n">
+        <v>773.5</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>10</v>
+      </c>
+      <c r="P11" t="n">
+        <v>286</v>
       </c>
     </row>
   </sheetData>
@@ -1006,7 +1066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1521,6 +1581,38 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Presión mínima</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1011.18 hPa</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>15/08/2026</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1013.55 hPa (2026-08-14)</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>TempMax 36.7°C / TempMin 24.2°C / Racha 24.6 km/h / Lluvia 0.0 mm / Presión 1011.18-1015.92 hPa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:P12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1053,6 +1053,66 @@
       </c>
       <c r="P11" t="n">
         <v>286</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>16/08/2026</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>22</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>04:29</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1016.59</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1013.55</v>
+      </c>
+      <c r="K12" t="n">
+        <v>89</v>
+      </c>
+      <c r="L12" t="n">
+        <v>35</v>
+      </c>
+      <c r="M12" t="n">
+        <v>895.7</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>11</v>
+      </c>
+      <c r="P12" t="n">
+        <v>287</v>
       </c>
     </row>
   </sheetData>
@@ -1066,7 +1126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1613,6 +1673,102 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Racha de viento</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>37.3 km/h</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>16/08/2026</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>04:29</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>36.5 km/h (2026-08-08)</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>TempMax 37.5°C / TempMin 22.0°C / Racha 37.3 km/h / Lluvia 0.0 mm / Presión 1013.55-1016.59 hPa</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Radiación solar</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>895.7 W/m²</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>16/08/2026</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>816.2 W/m² (2026-08-10)</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>TempMax 37.5°C / TempMin 22.0°C / Racha 37.3 km/h / Lluvia 0.0 mm / Presión 1013.55-1016.59 hPa</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Índice UV</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>11.0</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>16/08/2026</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>10.0  (2026-08-10)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>TempMax 37.5°C / TempMin 22.0°C / Racha 37.3 km/h / Lluvia 0.0 mm / Presión 1013.55-1016.59 hPa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P12"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1112,6 +1112,66 @@
         <v>11</v>
       </c>
       <c r="P12" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>23</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>05:14</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1018.29</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1015.24</v>
+      </c>
+      <c r="K13" t="n">
+        <v>86</v>
+      </c>
+      <c r="L13" t="n">
+        <v>35</v>
+      </c>
+      <c r="M13" t="n">
+        <v>753.5</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>9</v>
+      </c>
+      <c r="P13" t="n">
         <v>287</v>
       </c>
     </row>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:P14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1172,6 +1172,66 @@
         <v>9</v>
       </c>
       <c r="P13" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>18/08/2026</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>00:59</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1019.98</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1016.26</v>
+      </c>
+      <c r="K14" t="n">
+        <v>82</v>
+      </c>
+      <c r="L14" t="n">
+        <v>26</v>
+      </c>
+      <c r="M14" t="n">
+        <v>750.7</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>9</v>
+      </c>
+      <c r="P14" t="n">
         <v>287</v>
       </c>
     </row>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1232,6 +1232,66 @@
         <v>9</v>
       </c>
       <c r="P14" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>20</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>07:49</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1019.98</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1017.61</v>
+      </c>
+      <c r="K15" t="n">
+        <v>87</v>
+      </c>
+      <c r="L15" t="n">
+        <v>35</v>
+      </c>
+      <c r="M15" t="n">
+        <v>765</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>10</v>
+      </c>
+      <c r="P15" t="n">
         <v>287</v>
       </c>
     </row>
@@ -1246,7 +1306,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1889,6 +1949,38 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Temperatura mínima</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>20.0 °C</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>07:49</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>20.8 °C (2026-08-10)</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>TempMax 32.4°C / TempMin 20.0°C / Racha 26.1 km/h / Lluvia 0.0 mm / Presión 1017.61-1019.98 hPa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P15"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1292,6 +1292,66 @@
         <v>10</v>
       </c>
       <c r="P15" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>20/08/2026</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>02:39</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>18:19</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1019.64</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1016.93</v>
+      </c>
+      <c r="K16" t="n">
+        <v>89</v>
+      </c>
+      <c r="L16" t="n">
+        <v>40</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1055</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>14</v>
+      </c>
+      <c r="P16" t="n">
         <v>287</v>
       </c>
     </row>
@@ -1306,7 +1366,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1981,6 +2041,70 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Radiación solar</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1055.0 W/m²</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>20/08/2026</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>895.7 W/m² (2026-08-16)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>TempMax 29.2°C / TempMin 21.1°C / Racha 37.3 km/h / Lluvia 0.51 mm / Presión 1016.93-1019.64 hPa</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Índice UV</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>20/08/2026</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>11.0  (2026-08-16)</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>TempMax 29.2°C / TempMin 21.1°C / Racha 37.3 km/h / Lluvia 0.51 mm / Presión 1016.93-1019.64 hPa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P16"/>
+  <dimension ref="A1:P17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1352,6 +1352,66 @@
         <v>14</v>
       </c>
       <c r="P16" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>07:38</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>00:09</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1018.96</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1015.92</v>
+      </c>
+      <c r="K17" t="n">
+        <v>91</v>
+      </c>
+      <c r="L17" t="n">
+        <v>38</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1038</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>13</v>
+      </c>
+      <c r="P17" t="n">
         <v>287</v>
       </c>
     </row>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P17"/>
+  <dimension ref="A1:P18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1412,6 +1412,66 @@
         <v>13</v>
       </c>
       <c r="P17" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>03:59</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1017.61</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1015.24</v>
+      </c>
+      <c r="K18" t="n">
+        <v>87</v>
+      </c>
+      <c r="L18" t="n">
+        <v>44</v>
+      </c>
+      <c r="M18" t="n">
+        <v>776.4</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>10</v>
+      </c>
+      <c r="P18" t="n">
         <v>287</v>
       </c>
     </row>
@@ -1426,7 +1486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2165,6 +2225,38 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Temperatura mínima</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>19.2 °C</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>03:59</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>20.0 °C (2026-08-19)</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>TempMax 30.8°C / TempMin 19.2°C / Racha 33.3 km/h / Lluvia 0.0 mm / Presión 1015.24-1017.61 hPa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P18"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1472,6 +1472,66 @@
         <v>10</v>
       </c>
       <c r="P18" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>23/08/2026</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>07:29</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>19:14</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1018.96</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1016.59</v>
+      </c>
+      <c r="K19" t="n">
+        <v>90</v>
+      </c>
+      <c r="L19" t="n">
+        <v>40</v>
+      </c>
+      <c r="M19" t="n">
+        <v>796.2</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>10</v>
+      </c>
+      <c r="P19" t="n">
         <v>287</v>
       </c>
     </row>
@@ -1486,7 +1546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2257,6 +2317,38 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Temperatura mínima</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>18.3 °C</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>23/08/2026</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>07:29</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>19.2 °C (2026-08-22)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>TempMax 32.2°C / TempMin 18.3°C / Racha 31.7 km/h / Lluvia 0.0 mm / Presión 1016.59-1018.96 hPa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1532,6 +1532,66 @@
         <v>10</v>
       </c>
       <c r="P19" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1019.98</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1017.27</v>
+      </c>
+      <c r="K20" t="n">
+        <v>98</v>
+      </c>
+      <c r="L20" t="n">
+        <v>46</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1052.1</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>14</v>
+      </c>
+      <c r="P20" t="n">
         <v>287</v>
       </c>
     </row>
@@ -1546,7 +1606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2349,6 +2409,70 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Temperatura mínima</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>18.1 °C</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>18.3 °C (2026-08-23)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>TempMax 28.3°C / TempMin 18.1°C / Racha 39.8 km/h / Lluvia 1.78 mm / Presión 1017.27-1019.98 hPa</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Racha de viento</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>39.8 km/h</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>37.3 km/h (2026-08-16)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>TempMax 28.3°C / TempMin 18.1°C / Racha 39.8 km/h / Lluvia 1.78 mm / Presión 1017.27-1019.98 hPa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1592,6 +1592,66 @@
         <v>14</v>
       </c>
       <c r="P20" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>07:29</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>17:54</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1019.98</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1014.56</v>
+      </c>
+      <c r="K21" t="n">
+        <v>91</v>
+      </c>
+      <c r="L21" t="n">
+        <v>33</v>
+      </c>
+      <c r="M21" t="n">
+        <v>782</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>10</v>
+      </c>
+      <c r="P21" t="n">
         <v>287</v>
       </c>
     </row>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1652,6 +1652,66 @@
         <v>10</v>
       </c>
       <c r="P21" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>26/08/2026</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>04:44</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1017.61</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1014.56</v>
+      </c>
+      <c r="K22" t="n">
+        <v>88</v>
+      </c>
+      <c r="L22" t="n">
+        <v>37</v>
+      </c>
+      <c r="M22" t="n">
+        <v>969.7</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>12</v>
+      </c>
+      <c r="P22" t="n">
         <v>287</v>
       </c>
     </row>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1712,6 +1712,66 @@
         <v>12</v>
       </c>
       <c r="P22" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>06:39</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>17:19</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1022.35</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1016.59</v>
+      </c>
+      <c r="K23" t="n">
+        <v>98</v>
+      </c>
+      <c r="L23" t="n">
+        <v>37</v>
+      </c>
+      <c r="M23" t="n">
+        <v>995.4</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>13</v>
+      </c>
+      <c r="P23" t="n">
         <v>287</v>
       </c>
     </row>
@@ -1726,7 +1786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2593,6 +2653,38 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Presión máxima</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>1022.35 hPa</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>1019.98 hPa (2026-08-06)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>TempMax 26.6°C / TempMin 18.3°C / Racha 32.5 km/h / Lluvia 0.0 mm / Presión 1016.59-1022.35 hPa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P23"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1772,6 +1772,66 @@
         <v>13</v>
       </c>
       <c r="P23" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>17:54</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>05:09</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1022.69</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1019.98</v>
+      </c>
+      <c r="K24" t="n">
+        <v>83</v>
+      </c>
+      <c r="L24" t="n">
+        <v>18</v>
+      </c>
+      <c r="M24" t="n">
+        <v>767.7</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>10</v>
+      </c>
+      <c r="P24" t="n">
         <v>287</v>
       </c>
     </row>
@@ -1786,7 +1846,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2685,6 +2745,70 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Temperatura mínima</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>16.7 °C</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>05:09</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>18.1 °C (2026-08-24)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>TempMax 30.8°C / TempMin 16.7°C / Racha 28.5 km/h / Lluvia 0.0 mm / Presión 1019.98-1022.69 hPa</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Presión máxima</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>1022.69 hPa</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>1022.35 hPa (2026-08-27)</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>TempMax 30.8°C / TempMin 16.7°C / Racha 28.5 km/h / Lluvia 0.0 mm / Presión 1019.98-1022.69 hPa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P24"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1832,6 +1832,66 @@
         <v>10</v>
       </c>
       <c r="P24" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>17:34</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>02:14</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1021.67</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1017.95</v>
+      </c>
+      <c r="K25" t="n">
+        <v>67</v>
+      </c>
+      <c r="L25" t="n">
+        <v>14</v>
+      </c>
+      <c r="M25" t="n">
+        <v>802</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="O25" t="n">
+        <v>10</v>
+      </c>
+      <c r="P25" t="n">
         <v>287</v>
       </c>
     </row>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P25"/>
+  <dimension ref="A1:P26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1892,6 +1892,66 @@
         <v>10</v>
       </c>
       <c r="P25" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>19</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1019.98</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1017.61</v>
+      </c>
+      <c r="K26" t="n">
+        <v>44</v>
+      </c>
+      <c r="L26" t="n">
+        <v>18</v>
+      </c>
+      <c r="M26" t="n">
+        <v>756.5</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="O26" t="n">
+        <v>9</v>
+      </c>
+      <c r="P26" t="n">
         <v>287</v>
       </c>
     </row>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P26"/>
+  <dimension ref="A1:P27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1952,6 +1952,66 @@
         <v>9</v>
       </c>
       <c r="P26" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>17:19</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>07:04</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1019.98</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1017.27</v>
+      </c>
+      <c r="K27" t="n">
+        <v>56</v>
+      </c>
+      <c r="L27" t="n">
+        <v>16</v>
+      </c>
+      <c r="M27" t="n">
+        <v>745</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="O27" t="n">
+        <v>9</v>
+      </c>
+      <c r="P27" t="n">
         <v>287</v>
       </c>
     </row>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P27"/>
+  <dimension ref="A1:P28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2012,6 +2012,66 @@
         <v>9</v>
       </c>
       <c r="P27" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>05:54</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>20:09</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1021</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1017.61</v>
+      </c>
+      <c r="K28" t="n">
+        <v>63</v>
+      </c>
+      <c r="L28" t="n">
+        <v>25</v>
+      </c>
+      <c r="M28" t="n">
+        <v>705.2</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="O28" t="n">
+        <v>8</v>
+      </c>
+      <c r="P28" t="n">
         <v>287</v>
       </c>
     </row>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P28"/>
+  <dimension ref="A1:P29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2072,6 +2072,66 @@
         <v>8</v>
       </c>
       <c r="P28" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>01:39</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>18:14</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1021.67</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1019.64</v>
+      </c>
+      <c r="K29" t="n">
+        <v>79</v>
+      </c>
+      <c r="L29" t="n">
+        <v>25</v>
+      </c>
+      <c r="M29" t="n">
+        <v>736.5</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="O29" t="n">
+        <v>9</v>
+      </c>
+      <c r="P29" t="n">
         <v>287</v>
       </c>
     </row>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P29"/>
+  <dimension ref="A1:P30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2132,6 +2132,66 @@
         <v>9</v>
       </c>
       <c r="P29" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>06:39</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1022.35</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1019.98</v>
+      </c>
+      <c r="K30" t="n">
+        <v>66</v>
+      </c>
+      <c r="L30" t="n">
+        <v>11</v>
+      </c>
+      <c r="M30" t="n">
+        <v>719.5</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="O30" t="n">
+        <v>8</v>
+      </c>
+      <c r="P30" t="n">
         <v>287</v>
       </c>
     </row>
@@ -2146,7 +2206,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3109,6 +3169,38 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Temperatura máxima</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>44.5 °C</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>43.6 °C (2026-08-13)</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>TempMax 44.5°C / TempMin 24.7°C / Racha 19.8 km/h / Lluvia 0.0 mm / Presión 1019.98-1022.35 hPa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P30"/>
+  <dimension ref="A1:P31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2192,6 +2192,66 @@
         <v>8</v>
       </c>
       <c r="P30" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>17:49</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>23</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1023.37</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1019.64</v>
+      </c>
+      <c r="K31" t="n">
+        <v>74</v>
+      </c>
+      <c r="L31" t="n">
+        <v>23</v>
+      </c>
+      <c r="M31" t="n">
+        <v>918.5</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="O31" t="n">
+        <v>12</v>
+      </c>
+      <c r="P31" t="n">
         <v>287</v>
       </c>
     </row>
@@ -2206,7 +2266,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3201,6 +3261,38 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Presión máxima</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>1023.37 hPa</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>1022.69 hPa (2026-08-28)</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>TempMax 40.2°C / TempMin 23.1°C / Racha 23.0 km/h / Lluvia 0.0 mm / Presión 1019.64-1023.37 hPa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P31"/>
+  <dimension ref="A1:P32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2252,6 +2252,66 @@
         <v>12</v>
       </c>
       <c r="P31" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>05/09/2026</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>09:19</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>03:44</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1022.01</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1018.29</v>
+      </c>
+      <c r="K32" t="n">
+        <v>73</v>
+      </c>
+      <c r="L32" t="n">
+        <v>32</v>
+      </c>
+      <c r="M32" t="n">
+        <v>560.2</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="O32" t="n">
+        <v>6</v>
+      </c>
+      <c r="P32" t="n">
         <v>287</v>
       </c>
     </row>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P32"/>
+  <dimension ref="A1:P33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2312,6 +2312,66 @@
         <v>6</v>
       </c>
       <c r="P32" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>06/09/2026</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>04:34</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1022.69</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1019.98</v>
+      </c>
+      <c r="K33" t="n">
+        <v>57</v>
+      </c>
+      <c r="L33" t="n">
+        <v>15</v>
+      </c>
+      <c r="M33" t="n">
+        <v>750.7</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="O33" t="n">
+        <v>9</v>
+      </c>
+      <c r="P33" t="n">
         <v>287</v>
       </c>
     </row>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P33"/>
+  <dimension ref="A1:P34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2372,6 +2372,66 @@
         <v>9</v>
       </c>
       <c r="P33" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>07/09/2026</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>06:39</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1023.37</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1021</v>
+      </c>
+      <c r="K34" t="n">
+        <v>59</v>
+      </c>
+      <c r="L34" t="n">
+        <v>16</v>
+      </c>
+      <c r="M34" t="n">
+        <v>711</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="O34" t="n">
+        <v>9</v>
+      </c>
+      <c r="P34" t="n">
         <v>287</v>
       </c>
     </row>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P34"/>
+  <dimension ref="A1:P35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2432,6 +2432,66 @@
         <v>9</v>
       </c>
       <c r="P34" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>09:19</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>17:49</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1022.69</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1017.95</v>
+      </c>
+      <c r="K35" t="n">
+        <v>49</v>
+      </c>
+      <c r="L35" t="n">
+        <v>15</v>
+      </c>
+      <c r="M35" t="n">
+        <v>688.2</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="O35" t="n">
+        <v>8</v>
+      </c>
+      <c r="P35" t="n">
         <v>287</v>
       </c>
     </row>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P35"/>
+  <dimension ref="A1:P36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2492,6 +2492,66 @@
         <v>8</v>
       </c>
       <c r="P35" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>33</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>07:44</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1019.64</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1013.88</v>
+      </c>
+      <c r="K36" t="n">
+        <v>74</v>
+      </c>
+      <c r="L36" t="n">
+        <v>32</v>
+      </c>
+      <c r="M36" t="n">
+        <v>887.2</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="O36" t="n">
+        <v>11</v>
+      </c>
+      <c r="P36" t="n">
         <v>287</v>
       </c>
     </row>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P36"/>
+  <dimension ref="A1:P37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2552,6 +2552,66 @@
         <v>11</v>
       </c>
       <c r="P36" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>08:29</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1019.3</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1014.9</v>
+      </c>
+      <c r="K37" t="n">
+        <v>79</v>
+      </c>
+      <c r="L37" t="n">
+        <v>28</v>
+      </c>
+      <c r="M37" t="n">
+        <v>705.2</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="O37" t="n">
+        <v>8</v>
+      </c>
+      <c r="P37" t="n">
         <v>287</v>
       </c>
     </row>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P37"/>
+  <dimension ref="A1:P38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2612,6 +2612,66 @@
         <v>8</v>
       </c>
       <c r="P37" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>17:19</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>08:04</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>17:49</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1020.66</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1017.27</v>
+      </c>
+      <c r="K38" t="n">
+        <v>71</v>
+      </c>
+      <c r="L38" t="n">
+        <v>19</v>
+      </c>
+      <c r="M38" t="n">
+        <v>702.4</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="O38" t="n">
+        <v>8</v>
+      </c>
+      <c r="P38" t="n">
         <v>287</v>
       </c>
     </row>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P38"/>
+  <dimension ref="A1:P39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2672,6 +2672,66 @@
         <v>8</v>
       </c>
       <c r="P38" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>12/09/2026</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>22:04</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1020.32</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1017.61</v>
+      </c>
+      <c r="K39" t="n">
+        <v>48</v>
+      </c>
+      <c r="L39" t="n">
+        <v>19</v>
+      </c>
+      <c r="M39" t="n">
+        <v>691</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="O39" t="n">
+        <v>8</v>
+      </c>
+      <c r="P39" t="n">
         <v>287</v>
       </c>
     </row>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P39"/>
+  <dimension ref="A1:P40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2732,6 +2732,66 @@
         <v>8</v>
       </c>
       <c r="P39" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>13/09/2026</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>19:54</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1022.35</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1019.64</v>
+      </c>
+      <c r="K40" t="n">
+        <v>51</v>
+      </c>
+      <c r="L40" t="n">
+        <v>18</v>
+      </c>
+      <c r="M40" t="n">
+        <v>691</v>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="O40" t="n">
+        <v>8</v>
+      </c>
+      <c r="P40" t="n">
         <v>287</v>
       </c>
     </row>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P40"/>
+  <dimension ref="A1:P41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2792,6 +2792,66 @@
         <v>8</v>
       </c>
       <c r="P40" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>07:49</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1023.71</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1020.66</v>
+      </c>
+      <c r="K41" t="n">
+        <v>49</v>
+      </c>
+      <c r="L41" t="n">
+        <v>16</v>
+      </c>
+      <c r="M41" t="n">
+        <v>679.7</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="O41" t="n">
+        <v>8</v>
+      </c>
+      <c r="P41" t="n">
         <v>287</v>
       </c>
     </row>
@@ -2806,7 +2866,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3833,6 +3893,38 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Presión máxima</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>1023.71 hPa</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>1023.37 hPa (2026-09-04)</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>TempMax 36.9°C / TempMin 22.4°C / Racha 24.6 km/h / Lluvia 0.0 mm / Presión 1020.66-1023.71 hPa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P41"/>
+  <dimension ref="A1:P42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2852,6 +2852,66 @@
         <v>8</v>
       </c>
       <c r="P41" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>05:44</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1023.71</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1019.98</v>
+      </c>
+      <c r="K42" t="n">
+        <v>61</v>
+      </c>
+      <c r="L42" t="n">
+        <v>22</v>
+      </c>
+      <c r="M42" t="n">
+        <v>659.7</v>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="O42" t="n">
+        <v>8</v>
+      </c>
+      <c r="P42" t="n">
         <v>287</v>
       </c>
     </row>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P42"/>
+  <dimension ref="A1:P43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2912,6 +2912,66 @@
         <v>8</v>
       </c>
       <c r="P42" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>23:49</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1020.32</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1016.26</v>
+      </c>
+      <c r="K43" t="n">
+        <v>86</v>
+      </c>
+      <c r="L43" t="n">
+        <v>30</v>
+      </c>
+      <c r="M43" t="n">
+        <v>665.4</v>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="O43" t="n">
+        <v>8</v>
+      </c>
+      <c r="P43" t="n">
         <v>287</v>
       </c>
     </row>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P43"/>
+  <dimension ref="A1:P44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2972,6 +2972,66 @@
         <v>8</v>
       </c>
       <c r="P43" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>06:34</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>00:34</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>1018.29</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1015.24</v>
+      </c>
+      <c r="K44" t="n">
+        <v>88</v>
+      </c>
+      <c r="L44" t="n">
+        <v>35</v>
+      </c>
+      <c r="M44" t="n">
+        <v>747.9</v>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="O44" t="n">
+        <v>9</v>
+      </c>
+      <c r="P44" t="n">
         <v>287</v>
       </c>
     </row>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P44"/>
+  <dimension ref="A1:P45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3032,6 +3032,66 @@
         <v>9</v>
       </c>
       <c r="P44" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>17:34</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>07:09</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>1017.61</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1014.9</v>
+      </c>
+      <c r="K45" t="n">
+        <v>74</v>
+      </c>
+      <c r="L45" t="n">
+        <v>31</v>
+      </c>
+      <c r="M45" t="n">
+        <v>691</v>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="O45" t="n">
+        <v>9</v>
+      </c>
+      <c r="P45" t="n">
         <v>287</v>
       </c>
     </row>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P45"/>
+  <dimension ref="A1:P46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3092,6 +3092,66 @@
         <v>9</v>
       </c>
       <c r="P45" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>19/09/2026</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>03:19</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>23:34</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1020.66</v>
+      </c>
+      <c r="J46" t="n">
+        <v>1017.27</v>
+      </c>
+      <c r="K46" t="n">
+        <v>68</v>
+      </c>
+      <c r="L46" t="n">
+        <v>27</v>
+      </c>
+      <c r="M46" t="n">
+        <v>659.7</v>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="O46" t="n">
+        <v>8</v>
+      </c>
+      <c r="P46" t="n">
         <v>287</v>
       </c>
     </row>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P46"/>
+  <dimension ref="A1:P47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3152,6 +3152,66 @@
         <v>8</v>
       </c>
       <c r="P46" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>20/09/2026</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>05:44</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>23:09</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>1024.38</v>
+      </c>
+      <c r="J47" t="n">
+        <v>1020.66</v>
+      </c>
+      <c r="K47" t="n">
+        <v>55</v>
+      </c>
+      <c r="L47" t="n">
+        <v>31</v>
+      </c>
+      <c r="M47" t="n">
+        <v>642.7</v>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="O47" t="n">
+        <v>7</v>
+      </c>
+      <c r="P47" t="n">
         <v>287</v>
       </c>
     </row>
@@ -3166,7 +3226,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4225,6 +4285,38 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Presión máxima</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>1024.38 hPa</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>20/09/2026</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>1023.71 hPa (2026-09-14)</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>TempMax 33.1°C / TempMin 22.5°C / Racha 34.1 km/h / Lluvia 0.0 mm / Presión 1020.66-1024.38 hPa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P47"/>
+  <dimension ref="A1:P48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3213,6 +3213,66 @@
       </c>
       <c r="P47" t="n">
         <v>287</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>06:29</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>00:09</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>1025.74</v>
+      </c>
+      <c r="J48" t="n">
+        <v>1021.67</v>
+      </c>
+      <c r="K48" t="n">
+        <v>64</v>
+      </c>
+      <c r="L48" t="n">
+        <v>23</v>
+      </c>
+      <c r="M48" t="n">
+        <v>645.5</v>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="O48" t="n">
+        <v>7</v>
+      </c>
+      <c r="P48" t="n">
+        <v>286</v>
       </c>
     </row>
   </sheetData>
@@ -3226,7 +3286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4317,6 +4377,38 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Presión máxima</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>1025.74 hPa</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>1024.38 hPa (2026-09-20)</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>TempMax 35.8°C / TempMin 21.3°C / Racha 34.1 km/h / Lluvia 0.0 mm / Presión 1021.67-1025.74 hPa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P48"/>
+  <dimension ref="A1:P49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3272,6 +3272,66 @@
         <v>7</v>
       </c>
       <c r="P48" t="n">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>36</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>07:44</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>1022.69</v>
+      </c>
+      <c r="J49" t="n">
+        <v>1017.95</v>
+      </c>
+      <c r="K49" t="n">
+        <v>66</v>
+      </c>
+      <c r="L49" t="n">
+        <v>19</v>
+      </c>
+      <c r="M49" t="n">
+        <v>642.7</v>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="O49" t="n">
+        <v>7</v>
+      </c>
+      <c r="P49" t="n">
         <v>286</v>
       </c>
     </row>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P49"/>
+  <dimension ref="A1:P50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3333,6 +3333,66 @@
       </c>
       <c r="P49" t="n">
         <v>286</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>23/09/2026</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>08:39</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>1022.69</v>
+      </c>
+      <c r="J50" t="n">
+        <v>1019.64</v>
+      </c>
+      <c r="K50" t="n">
+        <v>67</v>
+      </c>
+      <c r="L50" t="n">
+        <v>17</v>
+      </c>
+      <c r="M50" t="n">
+        <v>631.2</v>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="O50" t="n">
+        <v>7</v>
+      </c>
+      <c r="P50" t="n">
+        <v>287</v>
       </c>
     </row>
   </sheetData>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P50"/>
+  <dimension ref="A1:P51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3392,6 +3392,66 @@
         <v>7</v>
       </c>
       <c r="P50" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>37</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>05:49</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
+        <v>1024.38</v>
+      </c>
+      <c r="J51" t="n">
+        <v>1020.66</v>
+      </c>
+      <c r="K51" t="n">
+        <v>51</v>
+      </c>
+      <c r="L51" t="n">
+        <v>17</v>
+      </c>
+      <c r="M51" t="n">
+        <v>628.5</v>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="O51" t="n">
+        <v>6</v>
+      </c>
+      <c r="P51" t="n">
         <v>287</v>
       </c>
     </row>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P51"/>
+  <dimension ref="A1:P52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3452,6 +3452,66 @@
         <v>6</v>
       </c>
       <c r="P51" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>38</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>22</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>04:49</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
+        <v>1022.69</v>
+      </c>
+      <c r="J52" t="n">
+        <v>1018.29</v>
+      </c>
+      <c r="K52" t="n">
+        <v>54</v>
+      </c>
+      <c r="L52" t="n">
+        <v>15</v>
+      </c>
+      <c r="M52" t="n">
+        <v>619.9</v>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="O52" t="n">
+        <v>6</v>
+      </c>
+      <c r="P52" t="n">
         <v>287</v>
       </c>
     </row>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P52"/>
+  <dimension ref="A1:P53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3512,6 +3512,66 @@
         <v>6</v>
       </c>
       <c r="P52" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>26/09/2026</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>40</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>25</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>01:24</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>18:44</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>1020.32</v>
+      </c>
+      <c r="J53" t="n">
+        <v>1017.27</v>
+      </c>
+      <c r="K53" t="n">
+        <v>43</v>
+      </c>
+      <c r="L53" t="n">
+        <v>11</v>
+      </c>
+      <c r="M53" t="n">
+        <v>617</v>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="O53" t="n">
+        <v>6</v>
+      </c>
+      <c r="P53" t="n">
         <v>287</v>
       </c>
     </row>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P53"/>
+  <dimension ref="A1:P54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3572,6 +3572,66 @@
         <v>6</v>
       </c>
       <c r="P53" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>27/09/2026</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>23:43</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>1019.64</v>
+      </c>
+      <c r="J54" t="n">
+        <v>1016.26</v>
+      </c>
+      <c r="K54" t="n">
+        <v>84</v>
+      </c>
+      <c r="L54" t="n">
+        <v>20</v>
+      </c>
+      <c r="M54" t="n">
+        <v>716.5</v>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="O54" t="n">
+        <v>8</v>
+      </c>
+      <c r="P54" t="n">
         <v>287</v>
       </c>
     </row>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P54"/>
+  <dimension ref="A1:P55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3632,6 +3632,66 @@
         <v>8</v>
       </c>
       <c r="P54" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>18:14</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>08:29</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>23</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="n">
+        <v>1019.64</v>
+      </c>
+      <c r="J55" t="n">
+        <v>1017.27</v>
+      </c>
+      <c r="K55" t="n">
+        <v>92</v>
+      </c>
+      <c r="L55" t="n">
+        <v>38</v>
+      </c>
+      <c r="M55" t="n">
+        <v>711</v>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="O55" t="n">
+        <v>8</v>
+      </c>
+      <c r="P55" t="n">
         <v>287</v>
       </c>
     </row>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P55"/>
+  <dimension ref="A1:P56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3692,6 +3692,66 @@
         <v>8</v>
       </c>
       <c r="P55" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>06:14</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>23</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>03:49</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>1019.98</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1017.27</v>
+      </c>
+      <c r="K56" t="n">
+        <v>77</v>
+      </c>
+      <c r="L56" t="n">
+        <v>33</v>
+      </c>
+      <c r="M56" t="n">
+        <v>645.5</v>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="O56" t="n">
+        <v>8</v>
+      </c>
+      <c r="P56" t="n">
         <v>287</v>
       </c>
     </row>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P56"/>
+  <dimension ref="A1:P57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3752,6 +3752,66 @@
         <v>8</v>
       </c>
       <c r="P56" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>18:29</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>08:59</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
+        <v>1021.67</v>
+      </c>
+      <c r="J57" t="n">
+        <v>1019.3</v>
+      </c>
+      <c r="K57" t="n">
+        <v>76</v>
+      </c>
+      <c r="L57" t="n">
+        <v>37</v>
+      </c>
+      <c r="M57" t="n">
+        <v>750.7</v>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="O57" t="n">
+        <v>9</v>
+      </c>
+      <c r="P57" t="n">
         <v>287</v>
       </c>
     </row>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P57"/>
+  <dimension ref="A1:P58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3812,6 +3812,66 @@
         <v>9</v>
       </c>
       <c r="P57" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>08:29</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>1022.01</v>
+      </c>
+      <c r="J58" t="n">
+        <v>1019.3</v>
+      </c>
+      <c r="K58" t="n">
+        <v>74</v>
+      </c>
+      <c r="L58" t="n">
+        <v>27</v>
+      </c>
+      <c r="M58" t="n">
+        <v>830.4</v>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="O58" t="n">
+        <v>10</v>
+      </c>
+      <c r="P58" t="n">
         <v>287</v>
       </c>
     </row>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P58"/>
+  <dimension ref="A1:P59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3873,6 +3873,66 @@
       </c>
       <c r="P58" t="n">
         <v>287</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>02/10/2026</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>19:04</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>08:24</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>19:24</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
+        <v>1022.01</v>
+      </c>
+      <c r="J59" t="n">
+        <v>1019.64</v>
+      </c>
+      <c r="K59" t="n">
+        <v>78</v>
+      </c>
+      <c r="L59" t="n">
+        <v>46</v>
+      </c>
+      <c r="M59" t="n">
+        <v>335.5</v>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="O59" t="n">
+        <v>3</v>
+      </c>
+      <c r="P59" t="n">
+        <v>195</v>
       </c>
     </row>
   </sheetData>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P59"/>
+  <dimension ref="A1:P60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3933,6 +3933,66 @@
       </c>
       <c r="P59" t="n">
         <v>195</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>03/10/2026</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>07:04</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
+        <v>1021.67</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1019.3</v>
+      </c>
+      <c r="K60" t="n">
+        <v>92</v>
+      </c>
+      <c r="L60" t="n">
+        <v>37</v>
+      </c>
+      <c r="M60" t="n">
+        <v>716.5</v>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="O60" t="n">
+        <v>9</v>
+      </c>
+      <c r="P60" t="n">
+        <v>287</v>
       </c>
     </row>
   </sheetData>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P60"/>
+  <dimension ref="A1:P61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3992,6 +3992,66 @@
         <v>9</v>
       </c>
       <c r="P60" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>04/10/2026</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>05:49</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="n">
+        <v>1021.67</v>
+      </c>
+      <c r="J61" t="n">
+        <v>1017.95</v>
+      </c>
+      <c r="K61" t="n">
+        <v>95</v>
+      </c>
+      <c r="L61" t="n">
+        <v>34</v>
+      </c>
+      <c r="M61" t="n">
+        <v>722.2</v>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="O61" t="n">
+        <v>8</v>
+      </c>
+      <c r="P61" t="n">
         <v>287</v>
       </c>
     </row>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P61"/>
+  <dimension ref="A1:P62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4052,6 +4052,66 @@
         <v>8</v>
       </c>
       <c r="P61" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>23:24</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>23:34</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="n">
+        <v>1022.35</v>
+      </c>
+      <c r="J62" t="n">
+        <v>1016.93</v>
+      </c>
+      <c r="K62" t="n">
+        <v>66</v>
+      </c>
+      <c r="L62" t="n">
+        <v>35</v>
+      </c>
+      <c r="M62" t="n">
+        <v>594.2</v>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="O62" t="n">
+        <v>6</v>
+      </c>
+      <c r="P62" t="n">
         <v>287</v>
       </c>
     </row>
@@ -4066,7 +4126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5189,6 +5249,38 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Racha de viento</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>44.6 km/h</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>23:34</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>39.8 km/h (2026-08-24)</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>TempMax 29.4°C / TempMin 22.2°C / Racha 44.6 km/h / Lluvia 0.0 mm / Presión 1016.93-1022.35 hPa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P62"/>
+  <dimension ref="A1:P63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4112,6 +4112,66 @@
         <v>6</v>
       </c>
       <c r="P62" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>23:44</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>00:14</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="n">
+        <v>1020.66</v>
+      </c>
+      <c r="J63" t="n">
+        <v>1015.92</v>
+      </c>
+      <c r="K63" t="n">
+        <v>80</v>
+      </c>
+      <c r="L63" t="n">
+        <v>38</v>
+      </c>
+      <c r="M63" t="n">
+        <v>739.4</v>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="O63" t="n">
+        <v>9</v>
+      </c>
+      <c r="P63" t="n">
         <v>287</v>
       </c>
     </row>
@@ -4126,7 +4186,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5281,6 +5341,38 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Racha de viento</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>45.4 km/h</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>00:14</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>44.6 km/h (2026-10-05)</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>TempMax 29.2°C / TempMin 21.3°C / Racha 45.4 km/h / Lluvia 0.0 mm / Presión 1015.92-1020.66 hPa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P63"/>
+  <dimension ref="A1:P64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4172,6 +4172,66 @@
         <v>9</v>
       </c>
       <c r="P63" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>07/10/2026</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="n">
+        <v>1019.98</v>
+      </c>
+      <c r="J64" t="n">
+        <v>1017.27</v>
+      </c>
+      <c r="K64" t="n">
+        <v>94</v>
+      </c>
+      <c r="L64" t="n">
+        <v>41</v>
+      </c>
+      <c r="M64" t="n">
+        <v>639.9</v>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="O64" t="n">
+        <v>8</v>
+      </c>
+      <c r="P64" t="n">
         <v>287</v>
       </c>
     </row>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P64"/>
+  <dimension ref="A1:P65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4232,6 +4232,66 @@
         <v>8</v>
       </c>
       <c r="P64" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>06:04</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>23:04</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" t="n">
+        <v>1021</v>
+      </c>
+      <c r="J65" t="n">
+        <v>1018.96</v>
+      </c>
+      <c r="K65" t="n">
+        <v>89</v>
+      </c>
+      <c r="L65" t="n">
+        <v>30</v>
+      </c>
+      <c r="M65" t="n">
+        <v>578.7</v>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="O65" t="n">
+        <v>6</v>
+      </c>
+      <c r="P65" t="n">
         <v>287</v>
       </c>
     </row>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P65"/>
+  <dimension ref="A1:P66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4292,6 +4292,66 @@
         <v>6</v>
       </c>
       <c r="P65" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>30</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>06:09</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="n">
+        <v>1022.35</v>
+      </c>
+      <c r="J66" t="n">
+        <v>1019.3</v>
+      </c>
+      <c r="K66" t="n">
+        <v>68</v>
+      </c>
+      <c r="L66" t="n">
+        <v>27</v>
+      </c>
+      <c r="M66" t="n">
+        <v>551.7</v>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="O66" t="n">
+        <v>6</v>
+      </c>
+      <c r="P66" t="n">
         <v>287</v>
       </c>
     </row>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P66"/>
+  <dimension ref="A1:P67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4352,6 +4352,66 @@
         <v>6</v>
       </c>
       <c r="P66" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>10/10/2026</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>08:04</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>19</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" t="n">
+        <v>1021.67</v>
+      </c>
+      <c r="J67" t="n">
+        <v>1017.95</v>
+      </c>
+      <c r="K67" t="n">
+        <v>78</v>
+      </c>
+      <c r="L67" t="n">
+        <v>29</v>
+      </c>
+      <c r="M67" t="n">
+        <v>575.9</v>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="O67" t="n">
+        <v>6</v>
+      </c>
+      <c r="P67" t="n">
         <v>287</v>
       </c>
     </row>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P67"/>
+  <dimension ref="A1:P68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4412,6 +4412,66 @@
         <v>6</v>
       </c>
       <c r="P67" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>11/10/2026</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>08:44</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>18:44</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" t="n">
+        <v>1019.98</v>
+      </c>
+      <c r="J68" t="n">
+        <v>1016.93</v>
+      </c>
+      <c r="K68" t="n">
+        <v>78</v>
+      </c>
+      <c r="L68" t="n">
+        <v>31</v>
+      </c>
+      <c r="M68" t="n">
+        <v>494.7</v>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="O68" t="n">
+        <v>5</v>
+      </c>
+      <c r="P68" t="n">
         <v>287</v>
       </c>
     </row>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P68"/>
+  <dimension ref="A1:P69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4472,6 +4472,66 @@
         <v>5</v>
       </c>
       <c r="P68" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>08:19</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" t="n">
+        <v>1022.69</v>
+      </c>
+      <c r="J69" t="n">
+        <v>1017.27</v>
+      </c>
+      <c r="K69" t="n">
+        <v>62</v>
+      </c>
+      <c r="L69" t="n">
+        <v>28</v>
+      </c>
+      <c r="M69" t="n">
+        <v>534.5</v>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="O69" t="n">
+        <v>5</v>
+      </c>
+      <c r="P69" t="n">
         <v>287</v>
       </c>
     </row>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P69"/>
+  <dimension ref="A1:P70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4532,6 +4532,66 @@
         <v>5</v>
       </c>
       <c r="P69" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>00:14</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" t="n">
+        <v>1026.08</v>
+      </c>
+      <c r="J70" t="n">
+        <v>1022.35</v>
+      </c>
+      <c r="K70" t="n">
+        <v>61</v>
+      </c>
+      <c r="L70" t="n">
+        <v>25</v>
+      </c>
+      <c r="M70" t="n">
+        <v>519</v>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="O70" t="n">
+        <v>5</v>
+      </c>
+      <c r="P70" t="n">
         <v>287</v>
       </c>
     </row>
@@ -4546,7 +4606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5733,6 +5793,38 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Presión máxima</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>1026.08 hPa</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>1025.74 hPa (2026-09-21)</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>TempMax 32.8°C / TempMin 20.6°C / Racha 15.8 km/h / Lluvia 0.0 mm / Presión 1022.35-1026.08 hPa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P70"/>
+  <dimension ref="A1:P71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4592,6 +4592,66 @@
         <v>5</v>
       </c>
       <c r="P70" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>20</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>04:59</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>22:49</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" t="n">
+        <v>1026.75</v>
+      </c>
+      <c r="J71" t="n">
+        <v>1023.71</v>
+      </c>
+      <c r="K71" t="n">
+        <v>62</v>
+      </c>
+      <c r="L71" t="n">
+        <v>26</v>
+      </c>
+      <c r="M71" t="n">
+        <v>519</v>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="O71" t="n">
+        <v>5</v>
+      </c>
+      <c r="P71" t="n">
         <v>287</v>
       </c>
     </row>
@@ -4606,7 +4666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5825,6 +5885,38 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Presión máxima</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>1026.75 hPa</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>1026.08 hPa (2026-10-13)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>TempMax 33.1°C / TempMin 20.0°C / Racha 35.7 km/h / Lluvia 0.0 mm / Presión 1023.71-1026.75 hPa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P71"/>
+  <dimension ref="A1:P72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4652,6 +4652,66 @@
         <v>5</v>
       </c>
       <c r="P71" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="H72" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" t="n">
+        <v>1025.06</v>
+      </c>
+      <c r="J72" t="n">
+        <v>1021.67</v>
+      </c>
+      <c r="K72" t="n">
+        <v>58</v>
+      </c>
+      <c r="L72" t="n">
+        <v>31</v>
+      </c>
+      <c r="M72" t="n">
+        <v>531.7</v>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="O72" t="n">
+        <v>5</v>
+      </c>
+      <c r="P72" t="n">
         <v>287</v>
       </c>
     </row>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P72"/>
+  <dimension ref="A1:P73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4712,6 +4712,66 @@
         <v>5</v>
       </c>
       <c r="P72" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>07:59</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
+      <c r="H73" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" t="n">
+        <v>1023.37</v>
+      </c>
+      <c r="J73" t="n">
+        <v>1020.32</v>
+      </c>
+      <c r="K73" t="n">
+        <v>74</v>
+      </c>
+      <c r="L73" t="n">
+        <v>31</v>
+      </c>
+      <c r="M73" t="n">
+        <v>496.2</v>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="O73" t="n">
+        <v>5</v>
+      </c>
+      <c r="P73" t="n">
         <v>287</v>
       </c>
     </row>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P73"/>
+  <dimension ref="A1:P74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4773,6 +4773,66 @@
       </c>
       <c r="P73" t="n">
         <v>287</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>17/10/2026</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>21:59</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>17:54</t>
+        </is>
+      </c>
+      <c r="H74" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="I74" t="n">
+        <v>1022.35</v>
+      </c>
+      <c r="J74" t="n">
+        <v>1015.24</v>
+      </c>
+      <c r="K74" t="n">
+        <v>87</v>
+      </c>
+      <c r="L74" t="n">
+        <v>44</v>
+      </c>
+      <c r="M74" t="n">
+        <v>560.2</v>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="O74" t="n">
+        <v>6</v>
+      </c>
+      <c r="P74" t="n">
+        <v>284</v>
       </c>
     </row>
   </sheetData>
@@ -4786,7 +4846,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6037,6 +6097,38 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Lluvia en un día</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>4.57 mm</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>17/10/2026</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>3.3 mm (2026-08-14)</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>TempMax 28.6°C / TempMin 17.6°C / Racha 27.7 km/h / Lluvia 4.57 mm / Presión 1015.24-1022.35 hPa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P74"/>
+  <dimension ref="A1:P75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4833,6 +4833,66 @@
       </c>
       <c r="P74" t="n">
         <v>284</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>18/10/2026</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>21:29</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>04:04</t>
+        </is>
+      </c>
+      <c r="H75" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" t="n">
+        <v>1015.92</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1012.53</v>
+      </c>
+      <c r="K75" t="n">
+        <v>96</v>
+      </c>
+      <c r="L75" t="n">
+        <v>59</v>
+      </c>
+      <c r="M75" t="n">
+        <v>492</v>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="O75" t="n">
+        <v>5</v>
+      </c>
+      <c r="P75" t="n">
+        <v>287</v>
       </c>
     </row>
   </sheetData>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P75"/>
+  <dimension ref="A1:P76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4892,6 +4892,66 @@
         <v>5</v>
       </c>
       <c r="P75" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>06:14</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="H76" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" t="n">
+        <v>1015.24</v>
+      </c>
+      <c r="J76" t="n">
+        <v>1012.19</v>
+      </c>
+      <c r="K76" t="n">
+        <v>90</v>
+      </c>
+      <c r="L76" t="n">
+        <v>49</v>
+      </c>
+      <c r="M76" t="n">
+        <v>605.7</v>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="O76" t="n">
+        <v>7</v>
+      </c>
+      <c r="P76" t="n">
         <v>287</v>
       </c>
     </row>
@@ -4906,7 +4966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6189,6 +6249,38 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Temperatura mínima</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>15.4 °C</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>06:14</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>16.7 °C (2026-08-28)</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>TempMax 24.9°C / TempMin 15.4°C / Racha 31.7 km/h / Lluvia 0.0 mm / Presión 1012.19-1015.24 hPa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P76"/>
+  <dimension ref="A1:P77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4952,6 +4952,66 @@
         <v>7</v>
       </c>
       <c r="P76" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>22:54</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" t="n">
+        <v>1021.67</v>
+      </c>
+      <c r="J77" t="n">
+        <v>1014.9</v>
+      </c>
+      <c r="K77" t="n">
+        <v>95</v>
+      </c>
+      <c r="L77" t="n">
+        <v>39</v>
+      </c>
+      <c r="M77" t="n">
+        <v>492</v>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="O77" t="n">
+        <v>5</v>
+      </c>
+      <c r="P77" t="n">
         <v>287</v>
       </c>
     </row>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P77"/>
+  <dimension ref="A1:T78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -498,6 +498,26 @@
           <t>Nº Observaciones</t>
         </is>
       </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Inicio Lluvia</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Fin Lluvia</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Intensidad Máx (mm/h)</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Hora Intensidad</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -544,7 +564,7 @@
       <c r="L2" t="n">
         <v>22</v>
       </c>
-      <c r="M2" t="n">
+      <c r="P2" t="n">
         <v>287</v>
       </c>
     </row>
@@ -593,7 +613,7 @@
       <c r="L3" t="n">
         <v>21</v>
       </c>
-      <c r="M3" t="n">
+      <c r="P3" t="n">
         <v>287</v>
       </c>
     </row>
@@ -642,7 +662,7 @@
       <c r="L4" t="n">
         <v>22</v>
       </c>
-      <c r="M4" t="n">
+      <c r="P4" t="n">
         <v>287</v>
       </c>
     </row>
@@ -691,7 +711,7 @@
       <c r="L5" t="n">
         <v>19</v>
       </c>
-      <c r="M5" t="n">
+      <c r="P5" t="n">
         <v>287</v>
       </c>
     </row>
@@ -5014,6 +5034,69 @@
       <c r="P77" t="n">
         <v>287</v>
       </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>21/10/2026</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>23</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>08:44</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>15</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>17:49</t>
+        </is>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" t="n">
+        <v>1026.41</v>
+      </c>
+      <c r="J78" t="n">
+        <v>1021.67</v>
+      </c>
+      <c r="K78" t="n">
+        <v>92</v>
+      </c>
+      <c r="L78" t="n">
+        <v>32</v>
+      </c>
+      <c r="M78" t="n">
+        <v>526</v>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="O78" t="n">
+        <v>5</v>
+      </c>
+      <c r="P78" t="n">
+        <v>287</v>
+      </c>
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr"/>
+      <c r="T78" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5026,7 +5109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6341,6 +6424,38 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Temperatura mínima</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>12.1 °C</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>21/10/2026</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>08:44</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>15.4 °C (2026-10-19)</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>TempMax 23.0°C / TempMin 12.1°C / Racha 15.0 km/h / Lluvia 0.0 mm / Presión 1021.67-1026.41 hPa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T78"/>
+  <dimension ref="A1:T79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5094,9 +5094,69 @@
       <c r="P78" t="n">
         <v>287</v>
       </c>
-      <c r="Q78" t="inlineStr"/>
-      <c r="R78" t="inlineStr"/>
-      <c r="T78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>15</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>05:59</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>19</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>19:59</t>
+        </is>
+      </c>
+      <c r="H79" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" t="n">
+        <v>1027.43</v>
+      </c>
+      <c r="J79" t="n">
+        <v>1024.72</v>
+      </c>
+      <c r="K79" t="n">
+        <v>75</v>
+      </c>
+      <c r="L79" t="n">
+        <v>26</v>
+      </c>
+      <c r="M79" t="n">
+        <v>520.4</v>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="O79" t="n">
+        <v>5</v>
+      </c>
+      <c r="P79" t="n">
+        <v>287</v>
+      </c>
+      <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr"/>
+      <c r="T79" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5109,7 +5169,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6456,6 +6516,38 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Presión máxima</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>1027.43 hPa</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>1026.75 hPa (2026-10-14)</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>TempMax 26.9°C / TempMin 15.0°C / Racha 19.0 km/h / Lluvia 0.0 mm / Presión 1024.72-1027.43 hPa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T79"/>
+  <dimension ref="A1:T80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5154,9 +5154,69 @@
       <c r="P79" t="n">
         <v>287</v>
       </c>
-      <c r="Q79" t="inlineStr"/>
-      <c r="R79" t="inlineStr"/>
-      <c r="T79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>18:03</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>06:04</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="H80" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" t="n">
+        <v>1028.45</v>
+      </c>
+      <c r="J80" t="n">
+        <v>1026.08</v>
+      </c>
+      <c r="K80" t="n">
+        <v>83</v>
+      </c>
+      <c r="L80" t="n">
+        <v>33</v>
+      </c>
+      <c r="M80" t="n">
+        <v>577.2</v>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="O80" t="n">
+        <v>6</v>
+      </c>
+      <c r="P80" t="n">
+        <v>287</v>
+      </c>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr"/>
+      <c r="T80" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5169,7 +5229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6548,6 +6608,38 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Presión máxima</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>1028.45 hPa</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1027.43 hPa (2026-10-22)</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>TempMax 24.7°C / TempMin 14.4°C / Racha 22.2 km/h / Lluvia 0.0 mm / Presión 1026.08-1028.45 hPa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T80"/>
+  <dimension ref="A1:T81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5214,9 +5214,69 @@
       <c r="P80" t="n">
         <v>287</v>
       </c>
-      <c r="Q80" t="inlineStr"/>
-      <c r="R80" t="inlineStr"/>
-      <c r="T80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>24/10/2026</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>17:54</t>
+        </is>
+      </c>
+      <c r="H81" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" t="n">
+        <v>1029.12</v>
+      </c>
+      <c r="J81" t="n">
+        <v>1026.41</v>
+      </c>
+      <c r="K81" t="n">
+        <v>82</v>
+      </c>
+      <c r="L81" t="n">
+        <v>24</v>
+      </c>
+      <c r="M81" t="n">
+        <v>510.3</v>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="O81" t="n">
+        <v>5</v>
+      </c>
+      <c r="P81" t="n">
+        <v>287</v>
+      </c>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr"/>
+      <c r="T81" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5229,7 +5289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6640,6 +6700,38 @@
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Presión máxima</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>1029.12 hPa</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>24/10/2026</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>1028.45 hPa (2026-10-23)</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>TempMax 26.4°C / TempMin 15.5°C / Racha 17.4 km/h / Lluvia 0.0 mm / Presión 1026.41-1029.12 hPa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T81"/>
+  <dimension ref="A1:T82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5274,9 +5274,69 @@
       <c r="P81" t="n">
         <v>287</v>
       </c>
-      <c r="Q81" t="inlineStr"/>
-      <c r="R81" t="inlineStr"/>
-      <c r="T81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>25/10/2026</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>07:34</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="H82" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" t="n">
+        <v>1028.11</v>
+      </c>
+      <c r="J82" t="n">
+        <v>1023.37</v>
+      </c>
+      <c r="K82" t="n">
+        <v>43</v>
+      </c>
+      <c r="L82" t="n">
+        <v>14</v>
+      </c>
+      <c r="M82" t="n">
+        <v>497.7</v>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="O82" t="n">
+        <v>5</v>
+      </c>
+      <c r="P82" t="n">
+        <v>299</v>
+      </c>
+      <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr"/>
+      <c r="T82" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T82"/>
+  <dimension ref="A1:T83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5334,9 +5334,69 @@
       <c r="P82" t="n">
         <v>299</v>
       </c>
-      <c r="Q82" t="inlineStr"/>
-      <c r="R82" t="inlineStr"/>
-      <c r="T82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>07:04</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>15</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>02:44</t>
+        </is>
+      </c>
+      <c r="H83" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" t="n">
+        <v>1023.03</v>
+      </c>
+      <c r="J83" t="n">
+        <v>1019.98</v>
+      </c>
+      <c r="K83" t="n">
+        <v>50</v>
+      </c>
+      <c r="L83" t="n">
+        <v>17</v>
+      </c>
+      <c r="M83" t="n">
+        <v>492</v>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="O83" t="n">
+        <v>5</v>
+      </c>
+      <c r="P83" t="n">
+        <v>287</v>
+      </c>
+      <c r="Q83" t="inlineStr"/>
+      <c r="R83" t="inlineStr"/>
+      <c r="T83" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T83"/>
+  <dimension ref="A1:T84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5394,9 +5394,69 @@
       <c r="P83" t="n">
         <v>287</v>
       </c>
-      <c r="Q83" t="inlineStr"/>
-      <c r="R83" t="inlineStr"/>
-      <c r="T83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>27/10/2026</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>05:54</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="H84" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" t="n">
+        <v>1024.38</v>
+      </c>
+      <c r="J84" t="n">
+        <v>1020.32</v>
+      </c>
+      <c r="K84" t="n">
+        <v>91</v>
+      </c>
+      <c r="L84" t="n">
+        <v>45</v>
+      </c>
+      <c r="M84" t="n">
+        <v>338.3</v>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="O84" t="n">
+        <v>3</v>
+      </c>
+      <c r="P84" t="n">
+        <v>287</v>
+      </c>
+      <c r="Q84" t="inlineStr"/>
+      <c r="R84" t="inlineStr"/>
+      <c r="T84" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T84"/>
+  <dimension ref="A1:T85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5454,9 +5454,69 @@
       <c r="P84" t="n">
         <v>287</v>
       </c>
-      <c r="Q84" t="inlineStr"/>
-      <c r="R84" t="inlineStr"/>
-      <c r="T84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>01:09</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>19</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="H85" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" t="n">
+        <v>1023.71</v>
+      </c>
+      <c r="J85" t="n">
+        <v>1021</v>
+      </c>
+      <c r="K85" t="n">
+        <v>94</v>
+      </c>
+      <c r="L85" t="n">
+        <v>25</v>
+      </c>
+      <c r="M85" t="n">
+        <v>476.2</v>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="O85" t="n">
+        <v>5</v>
+      </c>
+      <c r="P85" t="n">
+        <v>212</v>
+      </c>
+      <c r="Q85" t="inlineStr"/>
+      <c r="R85" t="inlineStr"/>
+      <c r="T85" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T85"/>
+  <dimension ref="A1:T86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5514,9 +5514,69 @@
       <c r="P85" t="n">
         <v>212</v>
       </c>
-      <c r="Q85" t="inlineStr"/>
-      <c r="R85" t="inlineStr"/>
-      <c r="T85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>29/10/2026</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>20</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>00:09</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>01:04</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>00:04</t>
+        </is>
+      </c>
+      <c r="H86" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" t="n">
+        <v>1022.69</v>
+      </c>
+      <c r="J86" t="n">
+        <v>1022.69</v>
+      </c>
+      <c r="K86" t="n">
+        <v>62</v>
+      </c>
+      <c r="L86" t="n">
+        <v>51</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>00:04</t>
+        </is>
+      </c>
+      <c r="O86" t="n">
+        <v>0</v>
+      </c>
+      <c r="P86" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q86" t="inlineStr"/>
+      <c r="R86" t="inlineStr"/>
+      <c r="T86" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/registro_meteo.xlsx
+++ b/registro_meteo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T86"/>
+  <dimension ref="A1:T87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5574,9 +5574,69 @@
       <c r="P86" t="n">
         <v>16</v>
       </c>
-      <c r="Q86" t="inlineStr"/>
-      <c r="R86" t="inlineStr"/>
-      <c r="T86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>30/10/2026</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>23:49</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>15</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="H87" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" t="n">
+        <v>1012.53</v>
+      </c>
+      <c r="J87" t="n">
+        <v>1011.18</v>
+      </c>
+      <c r="K87" t="n">
+        <v>62</v>
+      </c>
+      <c r="L87" t="n">
+        <v>27</v>
+      </c>
+      <c r="M87" t="n">
+        <v>500.5</v>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="O87" t="n">
+        <v>5</v>
+      </c>
+      <c r="P87" t="n">
+        <v>134</v>
+      </c>
+      <c r="Q87" t="inlineStr"/>
+      <c r="R87" t="inlineStr"/>
+      <c r="T87" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
